--- a/artfynd/A 38380-2024 artfynd.xlsx
+++ b/artfynd/A 38380-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130316982</v>
       </c>
       <c r="B2" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130316981</v>
       </c>
       <c r="B3" t="n">
-        <v>105899</v>
+        <v>105902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38380-2024 artfynd.xlsx
+++ b/artfynd/A 38380-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130316982</v>
       </c>
       <c r="B2" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130316981</v>
       </c>
       <c r="B3" t="n">
-        <v>105902</v>
+        <v>105928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38380-2024 artfynd.xlsx
+++ b/artfynd/A 38380-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130316982</v>
       </c>
       <c r="B2" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130316981</v>
       </c>
       <c r="B3" t="n">
-        <v>105928</v>
+        <v>105929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38380-2024 artfynd.xlsx
+++ b/artfynd/A 38380-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130316982</v>
       </c>
       <c r="B2" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130316981</v>
       </c>
       <c r="B3" t="n">
-        <v>105929</v>
+        <v>105930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38380-2024 artfynd.xlsx
+++ b/artfynd/A 38380-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130316982</v>
       </c>
       <c r="B2" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130316981</v>
       </c>
       <c r="B3" t="n">
-        <v>105930</v>
+        <v>105932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38380-2024 artfynd.xlsx
+++ b/artfynd/A 38380-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130316982</v>
       </c>
       <c r="B2" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130316981</v>
       </c>
       <c r="B3" t="n">
-        <v>105932</v>
+        <v>105936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
